--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2023/HAWAII_2023.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2023/HAWAII_2023.xlsx
@@ -351,40 +351,40 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D112"/>
+  <dimension ref="A1:D106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BAJA CALIFORNIA</t>
+          <t>Baja California</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MEXICALI</t>
+          <t>Mexicali</t>
         </is>
       </c>
       <c r="C2">
@@ -395,9 +395,14 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TECATE</t>
+          <t>Tecate</t>
         </is>
       </c>
       <c r="C3">
@@ -408,9 +413,14 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TIJUANA</t>
+          <t>Tijuana</t>
         </is>
       </c>
       <c r="C4">
@@ -421,9 +431,14 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C5">
@@ -436,12 +451,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAMPECHE</t>
+          <t>Campeche</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CHAMPOTÓN</t>
+          <t>Champotón</t>
         </is>
       </c>
       <c r="C6">
@@ -452,9 +467,14 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C7">
@@ -467,12 +487,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CHIAPAS</t>
+          <t>Chiapas</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ACAPETAHUA</t>
+          <t>Acapetahua</t>
         </is>
       </c>
       <c r="C8">
@@ -483,9 +503,14 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JIQUIPILAS</t>
+          <t>Jiquipilas</t>
         </is>
       </c>
       <c r="C9">
@@ -496,9 +521,14 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MAPASTEPEC</t>
+          <t>Mapastepec</t>
         </is>
       </c>
       <c r="C10">
@@ -509,9 +539,14 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PIJIJIAPAN</t>
+          <t>Pijijiapan</t>
         </is>
       </c>
       <c r="C11">
@@ -522,9 +557,14 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C12">
@@ -537,12 +577,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CHIHUAHUA</t>
+          <t>Chihuahua</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHIHUAHUA</t>
+          <t>Chihuahua</t>
         </is>
       </c>
       <c r="C13">
@@ -553,9 +593,14 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CUAUHTÉMOC</t>
+          <t>Cuauhtémoc</t>
         </is>
       </c>
       <c r="C14">
@@ -566,9 +611,14 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C15">
@@ -581,12 +631,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CIUDAD DE MÉXICO</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>AZCAPOTZALCO</t>
+          <t>Azcapotzalco</t>
         </is>
       </c>
       <c r="C16">
@@ -597,9 +647,14 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BENITO JUÁREZ</t>
+          <t>Benito Juárez</t>
         </is>
       </c>
       <c r="C17">
@@ -610,9 +665,14 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>COYOACÁN</t>
+          <t>Coyoacán</t>
         </is>
       </c>
       <c r="C18">
@@ -623,9 +683,14 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CUAUHTÉMOC</t>
+          <t>Cuauhtémoc</t>
         </is>
       </c>
       <c r="C19">
@@ -636,9 +701,14 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GUSTAVO A. MADERO</t>
+          <t>Gustavo A. Madero</t>
         </is>
       </c>
       <c r="C20">
@@ -649,9 +719,14 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IZTACALCO</t>
+          <t>Iztacalco</t>
         </is>
       </c>
       <c r="C21">
@@ -662,9 +737,14 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IZTAPALAPA</t>
+          <t>Iztapalapa</t>
         </is>
       </c>
       <c r="C22">
@@ -675,9 +755,14 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MIGUEL HIDALGO</t>
+          <t>Miguel Hidalgo</t>
         </is>
       </c>
       <c r="C23">
@@ -688,9 +773,14 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NO SE REGISTRÓ EL MUNICIPIO/CONDADO/ALCALDÍA DE NACIMIENTO</t>
+          <t>No Se Registró El Municipio/Condado/Alcaldía De Nacimiento</t>
         </is>
       </c>
       <c r="C24">
@@ -701,9 +791,14 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>VENUSTIANO CARRANZA</t>
+          <t>Venustiano Carranza</t>
         </is>
       </c>
       <c r="C25">
@@ -714,9 +809,14 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ÁLVARO OBREGÓN</t>
+          <t>Álvaro Obregón</t>
         </is>
       </c>
       <c r="C26">
@@ -727,9 +827,14 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C27">
@@ -742,12 +847,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DURANGO</t>
+          <t>Durango</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NAZAS</t>
+          <t>Nazas</t>
         </is>
       </c>
       <c r="C28">
@@ -758,9 +863,14 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C29">
@@ -773,12 +883,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ESTADO DE MÉXICO</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CHICOLOAPAN</t>
+          <t>Chicoloapan</t>
         </is>
       </c>
       <c r="C30">
@@ -789,9 +899,14 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NEZAHUALCÓYOTL</t>
+          <t>Nezahualcóyotl</t>
         </is>
       </c>
       <c r="C31">
@@ -802,9 +917,14 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>OZUMBA</t>
+          <t>Ozumba</t>
         </is>
       </c>
       <c r="C32">
@@ -815,9 +935,14 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SULTEPEC</t>
+          <t>Sultepec</t>
         </is>
       </c>
       <c r="C33">
@@ -828,9 +953,14 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TENANCINGO</t>
+          <t>Tenancingo</t>
         </is>
       </c>
       <c r="C34">
@@ -841,9 +971,14 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TOLUCA</t>
+          <t>Toluca</t>
         </is>
       </c>
       <c r="C35">
@@ -854,9 +989,14 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>VALLE DE CHALCO SOLIDARIDAD</t>
+          <t>Valle De Chalco Solidaridad</t>
         </is>
       </c>
       <c r="C36">
@@ -867,9 +1007,14 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C37">
@@ -882,12 +1027,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GUANAJUATO</t>
+          <t>Guanajuato</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SALVATIERRA</t>
+          <t>Salvatierra</t>
         </is>
       </c>
       <c r="C38">
@@ -898,9 +1043,14 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C39">
@@ -913,12 +1063,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GUERRERO</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BUENAVISTA DE CUÉLLAR</t>
+          <t>Buenavista De Cuéllar</t>
         </is>
       </c>
       <c r="C40">
@@ -929,9 +1079,14 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PUNGARABATO</t>
+          <t>Pungarabato</t>
         </is>
       </c>
       <c r="C41">
@@ -942,9 +1097,14 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C42">
@@ -957,12 +1117,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HIDALGO</t>
+          <t>Hidalgo</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ACAXOCHITLÁN</t>
+          <t>Acaxochitlán</t>
         </is>
       </c>
       <c r="C43">
@@ -973,9 +1133,14 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ACTOPAN</t>
+          <t>Actopan</t>
         </is>
       </c>
       <c r="C44">
@@ -986,9 +1151,14 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ATOTONILCO EL GRANDE</t>
+          <t>Atotonilco El Grande</t>
         </is>
       </c>
       <c r="C45">
@@ -999,9 +1169,14 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>METEPEC</t>
+          <t>Metepec</t>
         </is>
       </c>
       <c r="C46">
@@ -1012,9 +1187,14 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TULANCINGO DE BRAVO</t>
+          <t>Tulancingo De Bravo</t>
         </is>
       </c>
       <c r="C47">
@@ -1025,9 +1205,14 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C48">
@@ -1040,12 +1225,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>JALISCO</t>
+          <t>Jalisco</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ARANDAS</t>
+          <t>Arandas</t>
         </is>
       </c>
       <c r="C49">
@@ -1056,9 +1241,14 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AUTLÁN DE NAVARRO</t>
+          <t>Autlán De Navarro</t>
         </is>
       </c>
       <c r="C50">
@@ -1069,9 +1259,14 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CASIMIRO CASTILLO</t>
+          <t>Casimiro Castillo</t>
         </is>
       </c>
       <c r="C51">
@@ -1082,9 +1277,14 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GUADALAJARA</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="C52">
@@ -1095,9 +1295,14 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LA HUERTA</t>
+          <t>La Huerta</t>
         </is>
       </c>
       <c r="C53">
@@ -1108,9 +1313,14 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MAGDALENA</t>
+          <t>Magdalena</t>
         </is>
       </c>
       <c r="C54">
@@ -1121,9 +1331,14 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SAN PEDRO TLAQUEPAQUE</t>
+          <t>San Pedro Tlaquepaque</t>
         </is>
       </c>
       <c r="C55">
@@ -1134,9 +1349,14 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TONALÁ</t>
+          <t>Tonalá</t>
         </is>
       </c>
       <c r="C56">
@@ -1147,9 +1367,14 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TUXPAN</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C57">
@@ -1160,9 +1385,14 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C58">
@@ -1175,12 +1405,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MICHOACÁN DE OCAMPO</t>
+          <t>Michoacán De Ocampo</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LA PIEDAD</t>
+          <t>La Piedad</t>
         </is>
       </c>
       <c r="C59">
@@ -1191,9 +1421,14 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LOS REYES</t>
+          <t>Los Reyes</t>
         </is>
       </c>
       <c r="C60">
@@ -1204,9 +1439,14 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PURUÁNDIRO</t>
+          <t>Puruándiro</t>
         </is>
       </c>
       <c r="C61">
@@ -1217,9 +1457,14 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SALVADOR ESCALANTE</t>
+          <t>Salvador Escalante</t>
         </is>
       </c>
       <c r="C62">
@@ -1230,9 +1475,14 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VILLAMAR</t>
+          <t>Villamar</t>
         </is>
       </c>
       <c r="C63">
@@ -1243,9 +1493,14 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ZACAPU</t>
+          <t>Zacapu</t>
         </is>
       </c>
       <c r="C64">
@@ -1256,9 +1511,14 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ZAMORA</t>
+          <t>Zamora</t>
         </is>
       </c>
       <c r="C65">
@@ -1269,9 +1529,14 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Michoacán De Ocampo</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C66">
@@ -1284,12 +1549,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>NAYARIT</t>
+          <t>Nayarit</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LA YESCA</t>
+          <t>La Yesca</t>
         </is>
       </c>
       <c r="C67">
@@ -1300,9 +1565,14 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SAN BLAS</t>
+          <t>San Blas</t>
         </is>
       </c>
       <c r="C68">
@@ -1313,9 +1583,14 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SANTA MARÍA DEL ORO</t>
+          <t>Santa María Del Oro</t>
         </is>
       </c>
       <c r="C69">
@@ -1326,9 +1601,14 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TEPIC</t>
+          <t>Tepic</t>
         </is>
       </c>
       <c r="C70">
@@ -1339,9 +1619,14 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C71">
@@ -1354,12 +1639,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>OAXACA</t>
+          <t>Oaxaca</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CHALCATONGO DE HIDALGO</t>
+          <t>Chalcatongo De Hidalgo</t>
         </is>
       </c>
       <c r="C72">
@@ -1370,9 +1655,14 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HEROICA CIUDAD DE JUCHITÁN DE ZARAGOZA</t>
+          <t>Heroica Ciudad De Juchitán De Zaragoza</t>
         </is>
       </c>
       <c r="C73">
@@ -1383,9 +1673,14 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>HEROICA CIUDAD DE TLAXIACO</t>
+          <t>Heroica Ciudad De Tlaxiaco</t>
         </is>
       </c>
       <c r="C74">
@@ -1396,9 +1691,14 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PUTLA VILLA DE GUERRERO</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C75">
@@ -1409,9 +1709,14 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SAN ANDRÉS CABECERA NUEVA</t>
+          <t>San Andrés Cabecera Nueva</t>
         </is>
       </c>
       <c r="C76">
@@ -1422,9 +1727,14 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SAN FRANCISCO DEL MAR</t>
+          <t>San Francisco Del Mar</t>
         </is>
       </c>
       <c r="C77">
@@ -1435,9 +1745,14 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SANTA MARÍA CORTIJO</t>
+          <t>Santa María Cortijo</t>
         </is>
       </c>
       <c r="C78">
@@ -1448,9 +1763,14 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SANTIAGO JAMILTEPEC</t>
+          <t>Santiago Jamiltepec</t>
         </is>
       </c>
       <c r="C79">
@@ -1461,9 +1781,14 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SANTO DOMINGO TEHUANTEPEC</t>
+          <t>Santo Domingo Tehuantepec</t>
         </is>
       </c>
       <c r="C80">
@@ -1474,9 +1799,14 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SANTO TOMÁS OCOTEPEC</t>
+          <t>Santo Tomás Ocotepec</t>
         </is>
       </c>
       <c r="C81">
@@ -1487,9 +1817,14 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C82">
@@ -1502,12 +1837,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PUEBLA</t>
+          <t>Puebla</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LIBRES</t>
+          <t>Libres</t>
         </is>
       </c>
       <c r="C83">
@@ -1518,9 +1853,14 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>LOS REYES DE JUÁREZ</t>
+          <t>Los Reyes De Juárez</t>
         </is>
       </c>
       <c r="C84">
@@ -1531,9 +1871,14 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TETELA DE OCAMPO</t>
+          <t>Tetela De Ocampo</t>
         </is>
       </c>
       <c r="C85">
@@ -1544,9 +1889,14 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TLACHICHUCA</t>
+          <t>Tlachichuca</t>
         </is>
       </c>
       <c r="C86">
@@ -1557,9 +1907,14 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C87">
@@ -1572,12 +1927,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>QUERÉTARO</t>
+          <t>Querétaro</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>AMEALCO DE BONFIL</t>
+          <t>Amealco De Bonfil</t>
         </is>
       </c>
       <c r="C88">
@@ -1588,9 +1943,14 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CADEREYTA DE MONTES</t>
+          <t>Cadereyta De Montes</t>
         </is>
       </c>
       <c r="C89">
@@ -1601,9 +1961,14 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C90">
@@ -1616,12 +1981,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SAN LUIS POTOSÍ</t>
+          <t>San Luis Potosí</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TAMAZUNCHALE</t>
+          <t>Tamazunchale</t>
         </is>
       </c>
       <c r="C91">
@@ -1632,9 +1997,14 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C92">
@@ -1647,12 +2017,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SINALOA</t>
+          <t>Sinaloa</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EL FUERTE</t>
+          <t>El Fuerte</t>
         </is>
       </c>
       <c r="C93">
@@ -1663,9 +2033,14 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C94">
@@ -1678,12 +2053,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SONORA</t>
+          <t>Sonora</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>HERMOSILLO</t>
+          <t>Hermosillo</t>
         </is>
       </c>
       <c r="C95">
@@ -1694,9 +2069,14 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C96">
@@ -1709,12 +2089,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>TABASCO</t>
+          <t>Tabasco</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>JALAPA</t>
+          <t>Jalapa</t>
         </is>
       </c>
       <c r="C97">
@@ -1725,9 +2105,14 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C98">
@@ -1740,12 +2125,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>TLAXCALA</t>
+          <t>Tlaxcala</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>HUAMANTLA</t>
+          <t>Huamantla</t>
         </is>
       </c>
       <c r="C99">
@@ -1756,9 +2141,14 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C100">
@@ -1771,12 +2161,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
+          <t>Veracruz De Ignacio De La Llave</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PAPANTLA</t>
+          <t>Papantla</t>
         </is>
       </c>
       <c r="C101">
@@ -1787,9 +2177,14 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Veracruz De Ignacio De La Llave</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C102">
@@ -1802,12 +2197,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ZACATECAS</t>
+          <t>Zacatecas</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SAIN ALTO</t>
+          <t>Sain Alto</t>
         </is>
       </c>
       <c r="C103">
@@ -1818,9 +2213,14 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>VALPARAÍSO</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="C104">
@@ -1831,9 +2231,14 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C105">
@@ -1846,7 +2251,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="C106">
@@ -1854,41 +2259,6 @@
       </c>
       <c r="D106">
         <v>1</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 789,030</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de Mexicanas y Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Noviembre de 2024</t>
-        </is>
       </c>
     </row>
   </sheetData>
